--- a/Data/EXCEL/Transfer/salemon/202206/4581-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/4581-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5EE555D3-F5C3-497A-91FC-D236555165A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD98A13A-CE7B-485F-A53F-40CA8637EFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="4581-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -1218,20 +1218,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.25" customWidth="1"/>
-    <col min="2" max="5" width="11.125" customWidth="1"/>
-    <col min="6" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="8" width="11.125" customWidth="1"/>
-    <col min="9" max="10" width="10.5" customWidth="1"/>
-    <col min="11" max="11" width="11.125" customWidth="1"/>
-    <col min="12" max="12" width="10.5" customWidth="1"/>
-    <col min="13" max="13" width="11.125" customWidth="1"/>
-    <col min="14" max="15" width="10.5" customWidth="1"/>
-    <col min="16" max="16" width="11.125" customWidth="1"/>
-    <col min="17" max="17" width="11.5" customWidth="1"/>
+    <col min="1" max="1" width="15.125" customWidth="1"/>
+    <col min="2" max="5" width="12.625" customWidth="1"/>
+    <col min="6" max="7" width="12.125" customWidth="1"/>
+    <col min="8" max="8" width="12.625" customWidth="1"/>
+    <col min="9" max="10" width="12.125" customWidth="1"/>
+    <col min="11" max="11" width="12.625" customWidth="1"/>
+    <col min="12" max="12" width="12.125" customWidth="1"/>
+    <col min="13" max="13" width="12.625" customWidth="1"/>
+    <col min="14" max="15" width="12.125" customWidth="1"/>
+    <col min="16" max="16" width="12.625" customWidth="1"/>
+    <col min="17" max="17" width="13.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1384,1491 +1384,1491 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>33.9</v>
+        <v>31.7</v>
       </c>
       <c r="C5" s="7">
-        <v>31.7</v>
+        <v>30.3</v>
       </c>
       <c r="D5" s="7">
-        <v>35.450000000000003</v>
+        <v>32.35</v>
       </c>
       <c r="E5" s="7">
-        <v>29.75</v>
+        <v>30.05</v>
       </c>
       <c r="F5" s="8">
-        <v>-2.65</v>
+        <v>-1.4</v>
       </c>
       <c r="G5" s="8">
-        <v>-7.71</v>
+        <v>-4.42</v>
       </c>
       <c r="H5" s="9">
-        <v>0.90100000000000002</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="I5" s="10">
-        <v>22.1</v>
-      </c>
-      <c r="J5" s="10">
-        <v>9.9499999999999993</v>
+        <v>3.07</v>
+      </c>
+      <c r="J5" s="8">
+        <v>-5.53</v>
       </c>
       <c r="K5" s="9">
-        <v>3.95</v>
-      </c>
-      <c r="L5" s="9">
-        <v>0</v>
+        <v>4.87</v>
+      </c>
+      <c r="L5" s="8">
+        <v>-1.17</v>
       </c>
       <c r="M5" s="9">
-        <v>0.90100000000000002</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="N5" s="10">
-        <v>22.1</v>
-      </c>
-      <c r="O5" s="10">
-        <v>9.9499999999999993</v>
+        <v>3.07</v>
+      </c>
+      <c r="O5" s="8">
+        <v>-5.53</v>
       </c>
       <c r="P5" s="9">
-        <v>3.95</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>0</v>
+        <v>4.87</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>-1.17</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>35.85</v>
+        <v>33.9</v>
       </c>
       <c r="C6" s="7">
-        <v>34.35</v>
+        <v>31.7</v>
       </c>
       <c r="D6" s="7">
-        <v>36</v>
+        <v>35.450000000000003</v>
       </c>
       <c r="E6" s="7">
-        <v>34.35</v>
+        <v>29.75</v>
       </c>
       <c r="F6" s="8">
-        <v>-0.75</v>
+        <v>-2.65</v>
       </c>
       <c r="G6" s="8">
-        <v>-2.14</v>
+        <v>-7.71</v>
       </c>
       <c r="H6" s="9">
-        <v>0.73799999999999999</v>
-      </c>
-      <c r="I6" s="8">
-        <v>-3.3</v>
-      </c>
-      <c r="J6" s="8">
-        <v>-9.15</v>
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="I6" s="10">
+        <v>22.1</v>
+      </c>
+      <c r="J6" s="10">
+        <v>9.9499999999999993</v>
       </c>
       <c r="K6" s="9">
-        <v>3.05</v>
-      </c>
-      <c r="L6" s="8">
-        <v>-2.5499999999999998</v>
+        <v>3.95</v>
+      </c>
+      <c r="L6" s="9">
+        <v>0</v>
       </c>
       <c r="M6" s="9">
-        <v>0.73799999999999999</v>
-      </c>
-      <c r="N6" s="8">
-        <v>-3.3</v>
-      </c>
-      <c r="O6" s="8">
-        <v>-9.15</v>
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="N6" s="10">
+        <v>22.1</v>
+      </c>
+      <c r="O6" s="10">
+        <v>9.9499999999999993</v>
       </c>
       <c r="P6" s="9">
-        <v>3.05</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>-2.5499999999999998</v>
+        <v>3.95</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>35.049999999999997</v>
+        <v>35.85</v>
       </c>
       <c r="C7" s="7">
-        <v>35.1</v>
+        <v>34.35</v>
       </c>
       <c r="D7" s="7">
-        <v>36.299999999999997</v>
+        <v>36</v>
       </c>
       <c r="E7" s="7">
-        <v>34.549999999999997</v>
+        <v>34.35</v>
       </c>
       <c r="F7" s="8">
-        <v>-1.1499999999999999</v>
+        <v>-0.75</v>
       </c>
       <c r="G7" s="8">
-        <v>-3.17</v>
+        <v>-2.14</v>
       </c>
       <c r="H7" s="9">
-        <v>0.76300000000000001</v>
-      </c>
-      <c r="I7" s="10">
-        <v>10.5</v>
+        <v>0.73799999999999999</v>
+      </c>
+      <c r="I7" s="8">
+        <v>-3.3</v>
       </c>
       <c r="J7" s="8">
-        <v>-10.7</v>
+        <v>-9.15</v>
       </c>
       <c r="K7" s="9">
-        <v>2.31</v>
+        <v>3.05</v>
       </c>
       <c r="L7" s="8">
-        <v>-0.27</v>
+        <v>-2.5499999999999998</v>
       </c>
       <c r="M7" s="9">
-        <v>0.76300000000000001</v>
-      </c>
-      <c r="N7" s="10">
-        <v>10.5</v>
+        <v>0.73799999999999999</v>
+      </c>
+      <c r="N7" s="8">
+        <v>-3.3</v>
       </c>
       <c r="O7" s="8">
-        <v>-10.7</v>
+        <v>-9.15</v>
       </c>
       <c r="P7" s="9">
-        <v>2.31</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" s="8">
-        <v>-0.27</v>
+        <v>-2.5499999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>34.6</v>
+        <v>35.049999999999997</v>
       </c>
       <c r="C8" s="7">
-        <v>36.25</v>
+        <v>35.1</v>
       </c>
       <c r="D8" s="7">
-        <v>36.4</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="E8" s="7">
-        <v>34.6</v>
-      </c>
-      <c r="F8" s="10">
-        <v>1.6</v>
-      </c>
-      <c r="G8" s="10">
-        <v>4.62</v>
+        <v>34.549999999999997</v>
+      </c>
+      <c r="F8" s="8">
+        <v>-1.1499999999999999</v>
+      </c>
+      <c r="G8" s="8">
+        <v>-3.17</v>
       </c>
       <c r="H8" s="9">
-        <v>0.69</v>
-      </c>
-      <c r="I8" s="8">
-        <v>-18.8</v>
-      </c>
-      <c r="J8" s="10">
-        <v>5.38</v>
+        <v>0.76300000000000001</v>
+      </c>
+      <c r="I8" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="J8" s="8">
+        <v>-10.7</v>
       </c>
       <c r="K8" s="9">
-        <v>1.54</v>
-      </c>
-      <c r="L8" s="10">
-        <v>5.57</v>
+        <v>2.31</v>
+      </c>
+      <c r="L8" s="8">
+        <v>-0.27</v>
       </c>
       <c r="M8" s="9">
-        <v>0.69</v>
-      </c>
-      <c r="N8" s="8">
-        <v>-18.8</v>
-      </c>
-      <c r="O8" s="10">
-        <v>5.38</v>
+        <v>0.76300000000000001</v>
+      </c>
+      <c r="N8" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="O8" s="8">
+        <v>-10.7</v>
       </c>
       <c r="P8" s="9">
-        <v>1.54</v>
-      </c>
-      <c r="Q8" s="10">
-        <v>5.57</v>
+        <v>2.31</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>35.299999999999997</v>
+        <v>34.6</v>
       </c>
       <c r="C9" s="7">
-        <v>34.65</v>
+        <v>36.25</v>
       </c>
       <c r="D9" s="7">
-        <v>35.299999999999997</v>
+        <v>36.4</v>
       </c>
       <c r="E9" s="7">
-        <v>33.85</v>
-      </c>
-      <c r="F9" s="8">
-        <v>-0.65</v>
-      </c>
-      <c r="G9" s="8">
-        <v>-1.84</v>
+        <v>34.6</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="G9" s="10">
+        <v>4.62</v>
       </c>
       <c r="H9" s="9">
-        <v>0.85</v>
-      </c>
-      <c r="I9" s="10">
-        <v>2.5099999999999998</v>
+        <v>0.69</v>
+      </c>
+      <c r="I9" s="8">
+        <v>-18.8</v>
       </c>
       <c r="J9" s="10">
-        <v>5.78</v>
+        <v>5.38</v>
       </c>
       <c r="K9" s="9">
-        <v>0.85</v>
+        <v>1.54</v>
       </c>
       <c r="L9" s="10">
-        <v>5.78</v>
+        <v>5.57</v>
       </c>
       <c r="M9" s="9">
-        <v>0.85</v>
-      </c>
-      <c r="N9" s="10">
-        <v>2.5099999999999998</v>
+        <v>0.69</v>
+      </c>
+      <c r="N9" s="8">
+        <v>-18.8</v>
       </c>
       <c r="O9" s="10">
-        <v>5.78</v>
+        <v>5.38</v>
       </c>
       <c r="P9" s="9">
-        <v>0.85</v>
+        <v>1.54</v>
       </c>
       <c r="Q9" s="10">
-        <v>5.78</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>35.9</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="C10" s="7">
+        <v>34.65</v>
+      </c>
+      <c r="D10" s="7">
         <v>35.299999999999997</v>
       </c>
-      <c r="D10" s="7">
-        <v>36</v>
-      </c>
       <c r="E10" s="7">
-        <v>34.85</v>
+        <v>33.85</v>
       </c>
       <c r="F10" s="8">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="G10" s="8">
-        <v>-1.94</v>
+        <v>-1.84</v>
       </c>
       <c r="H10" s="9">
-        <v>0.82899999999999996</v>
-      </c>
-      <c r="I10" s="8">
-        <v>-4.5599999999999996</v>
+        <v>0.85</v>
+      </c>
+      <c r="I10" s="10">
+        <v>2.5099999999999998</v>
       </c>
       <c r="J10" s="10">
-        <v>9.42</v>
+        <v>5.78</v>
       </c>
       <c r="K10" s="9">
-        <v>10.039999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="L10" s="10">
-        <v>16.399999999999999</v>
+        <v>5.78</v>
       </c>
       <c r="M10" s="9">
-        <v>0.82899999999999996</v>
-      </c>
-      <c r="N10" s="8">
-        <v>-4.5599999999999996</v>
+        <v>0.85</v>
+      </c>
+      <c r="N10" s="10">
+        <v>2.5099999999999998</v>
       </c>
       <c r="O10" s="10">
-        <v>9.42</v>
+        <v>5.78</v>
       </c>
       <c r="P10" s="9">
-        <v>10.039999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="Q10" s="10">
-        <v>16.399999999999999</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
+        <v>35.9</v>
+      </c>
+      <c r="C11" s="7">
         <v>35.299999999999997</v>
       </c>
-      <c r="C11" s="7">
+      <c r="D11" s="7">
         <v>36</v>
       </c>
-      <c r="D11" s="7">
-        <v>36.1</v>
-      </c>
       <c r="E11" s="7">
-        <v>34.75</v>
-      </c>
-      <c r="F11" s="10">
-        <v>0.7</v>
-      </c>
-      <c r="G11" s="10">
-        <v>1.98</v>
+        <v>34.85</v>
+      </c>
+      <c r="F11" s="8">
+        <v>-0.7</v>
+      </c>
+      <c r="G11" s="8">
+        <v>-1.94</v>
       </c>
       <c r="H11" s="9">
-        <v>0.86899999999999999</v>
-      </c>
-      <c r="I11" s="10">
-        <v>2.95</v>
+        <v>0.82899999999999996</v>
+      </c>
+      <c r="I11" s="8">
+        <v>-4.5599999999999996</v>
       </c>
       <c r="J11" s="10">
-        <v>5.51</v>
+        <v>9.42</v>
       </c>
       <c r="K11" s="9">
-        <v>9.2100000000000009</v>
+        <v>10.039999999999999</v>
       </c>
       <c r="L11" s="10">
-        <v>17.100000000000001</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M11" s="9">
-        <v>0.86899999999999999</v>
-      </c>
-      <c r="N11" s="10">
-        <v>2.95</v>
+        <v>0.82899999999999996</v>
+      </c>
+      <c r="N11" s="8">
+        <v>-4.5599999999999996</v>
       </c>
       <c r="O11" s="10">
-        <v>5.51</v>
+        <v>9.42</v>
       </c>
       <c r="P11" s="9">
-        <v>9.2100000000000009</v>
+        <v>10.039999999999999</v>
       </c>
       <c r="Q11" s="10">
-        <v>17.100000000000001</v>
+        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>35.5</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="C12" s="7">
-        <v>35.299999999999997</v>
+        <v>36</v>
       </c>
       <c r="D12" s="7">
-        <v>35.75</v>
+        <v>36.1</v>
       </c>
       <c r="E12" s="7">
-        <v>33.950000000000003</v>
-      </c>
-      <c r="F12" s="8">
-        <v>-0.2</v>
-      </c>
-      <c r="G12" s="8">
-        <v>-0.56000000000000005</v>
+        <v>34.75</v>
+      </c>
+      <c r="F12" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="G12" s="10">
+        <v>1.98</v>
       </c>
       <c r="H12" s="9">
-        <v>0.84399999999999997</v>
-      </c>
-      <c r="I12" s="8">
-        <v>-2.67</v>
+        <v>0.86899999999999999</v>
+      </c>
+      <c r="I12" s="10">
+        <v>2.95</v>
       </c>
       <c r="J12" s="10">
-        <v>31.5</v>
+        <v>5.51</v>
       </c>
       <c r="K12" s="9">
-        <v>8.34</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="L12" s="10">
-        <v>18.5</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="M12" s="9">
-        <v>0.84399999999999997</v>
-      </c>
-      <c r="N12" s="8">
-        <v>-2.67</v>
+        <v>0.86899999999999999</v>
+      </c>
+      <c r="N12" s="10">
+        <v>2.95</v>
       </c>
       <c r="O12" s="10">
-        <v>31.5</v>
+        <v>5.51</v>
       </c>
       <c r="P12" s="9">
-        <v>8.34</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="Q12" s="10">
-        <v>18.5</v>
+        <v>17.100000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>36.6</v>
+        <v>35.5</v>
       </c>
       <c r="C13" s="7">
-        <v>35.5</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="D13" s="7">
-        <v>37</v>
+        <v>35.75</v>
       </c>
       <c r="E13" s="7">
-        <v>34.549999999999997</v>
+        <v>33.950000000000003</v>
       </c>
       <c r="F13" s="8">
-        <v>-0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="G13" s="8">
-        <v>-1.39</v>
+        <v>-0.56000000000000005</v>
       </c>
       <c r="H13" s="9">
-        <v>0.86699999999999999</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="I13" s="8">
-        <v>-8.69</v>
+        <v>-2.67</v>
       </c>
       <c r="J13" s="10">
-        <v>6.14</v>
+        <v>31.5</v>
       </c>
       <c r="K13" s="9">
-        <v>7.5</v>
+        <v>8.34</v>
       </c>
       <c r="L13" s="10">
-        <v>17.2</v>
+        <v>18.5</v>
       </c>
       <c r="M13" s="9">
-        <v>0.86699999999999999</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="N13" s="8">
-        <v>-8.69</v>
+        <v>-2.67</v>
       </c>
       <c r="O13" s="10">
-        <v>6.14</v>
+        <v>31.5</v>
       </c>
       <c r="P13" s="9">
-        <v>7.5</v>
+        <v>8.34</v>
       </c>
       <c r="Q13" s="10">
-        <v>17.2</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7">
-        <v>38.799999999999997</v>
+        <v>36.6</v>
       </c>
       <c r="C14" s="7">
-        <v>36</v>
+        <v>35.5</v>
       </c>
       <c r="D14" s="7">
-        <v>39.799999999999997</v>
+        <v>37</v>
       </c>
       <c r="E14" s="7">
-        <v>34.450000000000003</v>
+        <v>34.549999999999997</v>
       </c>
       <c r="F14" s="8">
-        <v>-2.8</v>
+        <v>-0.5</v>
       </c>
       <c r="G14" s="8">
-        <v>-7.22</v>
+        <v>-1.39</v>
       </c>
       <c r="H14" s="9">
-        <v>0.95</v>
-      </c>
-      <c r="I14" s="10">
-        <v>26</v>
+        <v>0.86699999999999999</v>
+      </c>
+      <c r="I14" s="8">
+        <v>-8.69</v>
       </c>
       <c r="J14" s="10">
-        <v>24.7</v>
+        <v>6.14</v>
       </c>
       <c r="K14" s="9">
-        <v>6.63</v>
+        <v>7.5</v>
       </c>
       <c r="L14" s="10">
-        <v>18.8</v>
+        <v>17.2</v>
       </c>
       <c r="M14" s="9">
-        <v>0.95</v>
-      </c>
-      <c r="N14" s="10">
-        <v>26</v>
+        <v>0.86699999999999999</v>
+      </c>
+      <c r="N14" s="8">
+        <v>-8.69</v>
       </c>
       <c r="O14" s="10">
-        <v>24.7</v>
+        <v>6.14</v>
       </c>
       <c r="P14" s="9">
-        <v>6.63</v>
+        <v>7.5</v>
       </c>
       <c r="Q14" s="10">
-        <v>18.8</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7">
-        <v>37.35</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="C15" s="7">
-        <v>38.799999999999997</v>
+        <v>36</v>
       </c>
       <c r="D15" s="7">
-        <v>41.35</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="E15" s="7">
-        <v>36.950000000000003</v>
-      </c>
-      <c r="F15" s="10">
-        <v>1.3</v>
-      </c>
-      <c r="G15" s="10">
-        <v>3.47</v>
+        <v>34.450000000000003</v>
+      </c>
+      <c r="F15" s="8">
+        <v>-2.8</v>
+      </c>
+      <c r="G15" s="8">
+        <v>-7.22</v>
       </c>
       <c r="H15" s="9">
-        <v>0.753</v>
-      </c>
-      <c r="I15" s="8">
-        <v>-23.3</v>
+        <v>0.95</v>
+      </c>
+      <c r="I15" s="10">
+        <v>26</v>
       </c>
       <c r="J15" s="10">
-        <v>19.600000000000001</v>
+        <v>24.7</v>
       </c>
       <c r="K15" s="9">
-        <v>5.68</v>
+        <v>6.63</v>
       </c>
       <c r="L15" s="10">
-        <v>17.899999999999999</v>
+        <v>18.8</v>
       </c>
       <c r="M15" s="9">
-        <v>0.753</v>
-      </c>
-      <c r="N15" s="8">
-        <v>-23.3</v>
+        <v>0.95</v>
+      </c>
+      <c r="N15" s="10">
+        <v>26</v>
       </c>
       <c r="O15" s="10">
-        <v>19.600000000000001</v>
+        <v>24.7</v>
       </c>
       <c r="P15" s="9">
-        <v>5.68</v>
+        <v>6.63</v>
       </c>
       <c r="Q15" s="10">
-        <v>17.899999999999999</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7">
-        <v>36.5</v>
+        <v>37.35</v>
       </c>
       <c r="C16" s="7">
-        <v>37.5</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="D16" s="7">
-        <v>37.9</v>
+        <v>41.35</v>
       </c>
       <c r="E16" s="7">
-        <v>35.6</v>
+        <v>36.950000000000003</v>
       </c>
       <c r="F16" s="10">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="G16" s="10">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="H16" s="9">
-        <v>0.98299999999999998</v>
-      </c>
-      <c r="I16" s="10">
-        <v>20</v>
+        <v>0.753</v>
+      </c>
+      <c r="I16" s="8">
+        <v>-23.3</v>
       </c>
       <c r="J16" s="10">
-        <v>33.4</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="K16" s="9">
-        <v>4.93</v>
+        <v>5.68</v>
       </c>
       <c r="L16" s="10">
-        <v>17.600000000000001</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="M16" s="9">
-        <v>0.98299999999999998</v>
-      </c>
-      <c r="N16" s="10">
-        <v>20</v>
+        <v>0.753</v>
+      </c>
+      <c r="N16" s="8">
+        <v>-23.3</v>
       </c>
       <c r="O16" s="10">
-        <v>33.4</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="P16" s="9">
-        <v>4.93</v>
+        <v>5.68</v>
       </c>
       <c r="Q16" s="10">
-        <v>17.600000000000001</v>
+        <v>17.899999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7">
-        <v>39.1</v>
+        <v>36.5</v>
       </c>
       <c r="C17" s="7">
-        <v>36.25</v>
+        <v>37.5</v>
       </c>
       <c r="D17" s="7">
-        <v>39.15</v>
+        <v>37.9</v>
       </c>
       <c r="E17" s="7">
-        <v>34.75</v>
-      </c>
-      <c r="F17" s="8">
-        <v>-2.8</v>
-      </c>
-      <c r="G17" s="8">
-        <v>-7.17</v>
+        <v>35.6</v>
+      </c>
+      <c r="F17" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="G17" s="10">
+        <v>3.45</v>
       </c>
       <c r="H17" s="9">
-        <v>0.81899999999999995</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="I17" s="10">
-        <v>0.85</v>
+        <v>20</v>
       </c>
       <c r="J17" s="10">
-        <v>52.2</v>
+        <v>33.4</v>
       </c>
       <c r="K17" s="9">
-        <v>3.94</v>
+        <v>4.93</v>
       </c>
       <c r="L17" s="10">
-        <v>14.1</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="M17" s="9">
-        <v>0.81899999999999995</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="N17" s="10">
-        <v>0.85</v>
+        <v>20</v>
       </c>
       <c r="O17" s="10">
-        <v>52.2</v>
+        <v>33.4</v>
       </c>
       <c r="P17" s="9">
-        <v>3.94</v>
+        <v>4.93</v>
       </c>
       <c r="Q17" s="10">
-        <v>14.1</v>
+        <v>17.600000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7">
-        <v>39.65</v>
+        <v>39.1</v>
       </c>
       <c r="C18" s="7">
-        <v>39.049999999999997</v>
+        <v>36.25</v>
       </c>
       <c r="D18" s="7">
-        <v>41.3</v>
+        <v>39.15</v>
       </c>
       <c r="E18" s="7">
-        <v>38.35</v>
+        <v>34.75</v>
       </c>
       <c r="F18" s="8">
-        <v>-0.6</v>
+        <v>-2.8</v>
       </c>
       <c r="G18" s="8">
-        <v>-1.51</v>
+        <v>-7.17</v>
       </c>
       <c r="H18" s="9">
-        <v>0.81200000000000006</v>
-      </c>
-      <c r="I18" s="8">
-        <v>-4.9400000000000004</v>
+        <v>0.81899999999999995</v>
+      </c>
+      <c r="I18" s="10">
+        <v>0.85</v>
       </c>
       <c r="J18" s="10">
-        <v>33.5</v>
+        <v>52.2</v>
       </c>
       <c r="K18" s="9">
-        <v>3.13</v>
+        <v>3.94</v>
       </c>
       <c r="L18" s="10">
-        <v>7.09</v>
+        <v>14.1</v>
       </c>
       <c r="M18" s="9">
-        <v>0.81200000000000006</v>
-      </c>
-      <c r="N18" s="8">
-        <v>-4.9400000000000004</v>
+        <v>0.81899999999999995</v>
+      </c>
+      <c r="N18" s="10">
+        <v>0.85</v>
       </c>
       <c r="O18" s="10">
-        <v>33.5</v>
+        <v>52.2</v>
       </c>
       <c r="P18" s="9">
-        <v>3.13</v>
+        <v>3.94</v>
       </c>
       <c r="Q18" s="10">
-        <v>7.09</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7">
-        <v>37.5</v>
+        <v>39.65</v>
       </c>
       <c r="C19" s="7">
-        <v>39.65</v>
+        <v>39.049999999999997</v>
       </c>
       <c r="D19" s="7">
-        <v>43.75</v>
+        <v>41.3</v>
       </c>
       <c r="E19" s="7">
-        <v>37.25</v>
-      </c>
-      <c r="F19" s="10">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="G19" s="10">
-        <v>6.59</v>
+        <v>38.35</v>
+      </c>
+      <c r="F19" s="8">
+        <v>-0.6</v>
+      </c>
+      <c r="G19" s="8">
+        <v>-1.51</v>
       </c>
       <c r="H19" s="9">
-        <v>0.85499999999999998</v>
-      </c>
-      <c r="I19" s="10">
-        <v>30.4</v>
-      </c>
-      <c r="J19" s="8">
-        <v>-4.6399999999999997</v>
+        <v>0.81200000000000006</v>
+      </c>
+      <c r="I19" s="8">
+        <v>-4.9400000000000004</v>
+      </c>
+      <c r="J19" s="10">
+        <v>33.5</v>
       </c>
       <c r="K19" s="9">
-        <v>2.31</v>
+        <v>3.13</v>
       </c>
       <c r="L19" s="10">
-        <v>0.11</v>
+        <v>7.09</v>
       </c>
       <c r="M19" s="9">
-        <v>0.85499999999999998</v>
-      </c>
-      <c r="N19" s="10">
-        <v>30.4</v>
-      </c>
-      <c r="O19" s="8">
-        <v>-4.6399999999999997</v>
+        <v>0.81200000000000006</v>
+      </c>
+      <c r="N19" s="8">
+        <v>-4.9400000000000004</v>
+      </c>
+      <c r="O19" s="10">
+        <v>33.5</v>
       </c>
       <c r="P19" s="9">
-        <v>2.31</v>
+        <v>3.13</v>
       </c>
       <c r="Q19" s="10">
-        <v>0.11</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7">
-        <v>35.799999999999997</v>
+        <v>37.5</v>
       </c>
       <c r="C20" s="7">
-        <v>37.200000000000003</v>
+        <v>39.65</v>
       </c>
       <c r="D20" s="7">
-        <v>38.5</v>
+        <v>43.75</v>
       </c>
       <c r="E20" s="7">
-        <v>35</v>
+        <v>37.25</v>
       </c>
       <c r="F20" s="10">
-        <v>0.2</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="G20" s="10">
-        <v>0.54</v>
+        <v>6.59</v>
       </c>
       <c r="H20" s="9">
-        <v>0.65500000000000003</v>
-      </c>
-      <c r="I20" s="8">
-        <v>-18.5</v>
-      </c>
-      <c r="J20" s="10">
-        <v>4.33</v>
+        <v>0.85499999999999998</v>
+      </c>
+      <c r="I20" s="10">
+        <v>30.4</v>
+      </c>
+      <c r="J20" s="8">
+        <v>-4.6399999999999997</v>
       </c>
       <c r="K20" s="9">
-        <v>1.46</v>
+        <v>2.31</v>
       </c>
       <c r="L20" s="10">
-        <v>3.12</v>
+        <v>0.11</v>
       </c>
       <c r="M20" s="9">
-        <v>0.65500000000000003</v>
-      </c>
-      <c r="N20" s="8">
-        <v>-18.5</v>
-      </c>
-      <c r="O20" s="10">
-        <v>4.33</v>
+        <v>0.85499999999999998</v>
+      </c>
+      <c r="N20" s="10">
+        <v>30.4</v>
+      </c>
+      <c r="O20" s="8">
+        <v>-4.6399999999999997</v>
       </c>
       <c r="P20" s="9">
-        <v>1.46</v>
+        <v>2.31</v>
       </c>
       <c r="Q20" s="10">
-        <v>3.12</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7">
-        <v>37.299999999999997</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="C21" s="7">
-        <v>37</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="D21" s="7">
-        <v>40.700000000000003</v>
+        <v>38.5</v>
       </c>
       <c r="E21" s="7">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="F21" s="8">
-        <v>-0.2</v>
-      </c>
-      <c r="G21" s="8">
-        <v>-0.54</v>
+        <v>35</v>
+      </c>
+      <c r="F21" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="G21" s="10">
+        <v>0.54</v>
       </c>
       <c r="H21" s="9">
-        <v>0.80400000000000005</v>
-      </c>
-      <c r="I21" s="10">
-        <v>6.04</v>
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="I21" s="8">
+        <v>-18.5</v>
       </c>
       <c r="J21" s="10">
-        <v>2.23</v>
+        <v>4.33</v>
       </c>
       <c r="K21" s="9">
-        <v>0.80400000000000005</v>
+        <v>1.46</v>
       </c>
       <c r="L21" s="10">
-        <v>2.23</v>
+        <v>3.12</v>
       </c>
       <c r="M21" s="9">
-        <v>0.80400000000000005</v>
-      </c>
-      <c r="N21" s="10">
-        <v>6.04</v>
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="N21" s="8">
+        <v>-18.5</v>
       </c>
       <c r="O21" s="10">
-        <v>2.23</v>
+        <v>4.33</v>
       </c>
       <c r="P21" s="9">
-        <v>0.80400000000000005</v>
+        <v>1.46</v>
       </c>
       <c r="Q21" s="10">
-        <v>2.23</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7">
-        <v>37.35</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="C22" s="7">
-        <v>37.200000000000003</v>
+        <v>37</v>
       </c>
       <c r="D22" s="7">
-        <v>37.950000000000003</v>
+        <v>40.700000000000003</v>
       </c>
       <c r="E22" s="7">
-        <v>36.4</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="F22" s="8">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="G22" s="8">
-        <v>-0.27</v>
+        <v>-0.54</v>
       </c>
       <c r="H22" s="9">
-        <v>0.75800000000000001</v>
-      </c>
-      <c r="I22" s="8">
-        <v>-7.97</v>
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="I22" s="10">
+        <v>6.04</v>
       </c>
       <c r="J22" s="10">
-        <v>0.03</v>
+        <v>2.23</v>
       </c>
       <c r="K22" s="9">
-        <v>8.6300000000000008</v>
-      </c>
-      <c r="L22" s="8">
-        <v>-16.7</v>
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="L22" s="10">
+        <v>2.23</v>
       </c>
       <c r="M22" s="9">
-        <v>0.75800000000000001</v>
-      </c>
-      <c r="N22" s="8">
-        <v>-7.97</v>
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="N22" s="10">
+        <v>6.04</v>
       </c>
       <c r="O22" s="10">
-        <v>0.03</v>
+        <v>2.23</v>
       </c>
       <c r="P22" s="9">
-        <v>8.6300000000000008</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>-16.7</v>
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="Q22" s="10">
+        <v>2.23</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7">
-        <v>36.700000000000003</v>
+        <v>37.35</v>
       </c>
       <c r="C23" s="7">
-        <v>37.299999999999997</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="D23" s="7">
-        <v>38.5</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="E23" s="7">
-        <v>36</v>
-      </c>
-      <c r="F23" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="G23" s="10">
-        <v>1.63</v>
+        <v>36.4</v>
+      </c>
+      <c r="F23" s="8">
+        <v>-0.1</v>
+      </c>
+      <c r="G23" s="8">
+        <v>-0.27</v>
       </c>
       <c r="H23" s="9">
-        <v>0.82399999999999995</v>
-      </c>
-      <c r="I23" s="10">
-        <v>28.3</v>
-      </c>
-      <c r="J23" s="8">
-        <v>-1.84</v>
+        <v>0.75800000000000001</v>
+      </c>
+      <c r="I23" s="8">
+        <v>-7.97</v>
+      </c>
+      <c r="J23" s="10">
+        <v>0.03</v>
       </c>
       <c r="K23" s="9">
-        <v>7.87</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="L23" s="8">
-        <v>-18.100000000000001</v>
+        <v>-16.7</v>
       </c>
       <c r="M23" s="9">
-        <v>0.82399999999999995</v>
-      </c>
-      <c r="N23" s="10">
-        <v>28.3</v>
-      </c>
-      <c r="O23" s="8">
-        <v>-1.84</v>
+        <v>0.75800000000000001</v>
+      </c>
+      <c r="N23" s="8">
+        <v>-7.97</v>
+      </c>
+      <c r="O23" s="10">
+        <v>0.03</v>
       </c>
       <c r="P23" s="9">
-        <v>7.87</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="Q23" s="8">
-        <v>-18.100000000000001</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="C24" s="7">
         <v>37.299999999999997</v>
       </c>
-      <c r="C24" s="7">
-        <v>36.700000000000003</v>
-      </c>
       <c r="D24" s="7">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="E24" s="7">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="F24" s="8">
-        <v>-0.8</v>
-      </c>
-      <c r="G24" s="8">
-        <v>-2.13</v>
+        <v>36</v>
+      </c>
+      <c r="F24" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="G24" s="10">
+        <v>1.63</v>
       </c>
       <c r="H24" s="9">
-        <v>0.64200000000000002</v>
-      </c>
-      <c r="I24" s="8">
-        <v>-21.4</v>
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="I24" s="10">
+        <v>28.3</v>
       </c>
       <c r="J24" s="8">
-        <v>-0.99</v>
+        <v>-1.84</v>
       </c>
       <c r="K24" s="9">
-        <v>7.04</v>
+        <v>7.87</v>
       </c>
       <c r="L24" s="8">
-        <v>-19.7</v>
+        <v>-18.100000000000001</v>
       </c>
       <c r="M24" s="9">
-        <v>0.64200000000000002</v>
-      </c>
-      <c r="N24" s="8">
-        <v>-21.4</v>
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="N24" s="10">
+        <v>28.3</v>
       </c>
       <c r="O24" s="8">
-        <v>-0.99</v>
+        <v>-1.84</v>
       </c>
       <c r="P24" s="9">
-        <v>7.04</v>
+        <v>7.87</v>
       </c>
       <c r="Q24" s="8">
-        <v>-19.7</v>
+        <v>-18.100000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B25" s="7">
-        <v>37</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="C25" s="7">
-        <v>37.5</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="D25" s="7">
-        <v>38.049999999999997</v>
+        <v>38</v>
       </c>
       <c r="E25" s="7">
         <v>36.200000000000003</v>
       </c>
-      <c r="F25" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="G25" s="10">
-        <v>1.35</v>
+      <c r="F25" s="8">
+        <v>-0.8</v>
+      </c>
+      <c r="G25" s="8">
+        <v>-2.13</v>
       </c>
       <c r="H25" s="9">
-        <v>0.81699999999999995</v>
-      </c>
-      <c r="I25" s="10">
-        <v>7.29</v>
-      </c>
-      <c r="J25" s="10">
-        <v>9.4700000000000006</v>
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="I25" s="8">
+        <v>-21.4</v>
+      </c>
+      <c r="J25" s="8">
+        <v>-0.99</v>
       </c>
       <c r="K25" s="9">
-        <v>6.4</v>
+        <v>7.04</v>
       </c>
       <c r="L25" s="8">
-        <v>-21.2</v>
+        <v>-19.7</v>
       </c>
       <c r="M25" s="9">
-        <v>0.81699999999999995</v>
-      </c>
-      <c r="N25" s="10">
-        <v>7.29</v>
-      </c>
-      <c r="O25" s="10">
-        <v>9.4700000000000006</v>
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="N25" s="8">
+        <v>-21.4</v>
+      </c>
+      <c r="O25" s="8">
+        <v>-0.99</v>
       </c>
       <c r="P25" s="9">
-        <v>6.4</v>
+        <v>7.04</v>
       </c>
       <c r="Q25" s="8">
-        <v>-21.2</v>
+        <v>-19.7</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B26" s="7">
         <v>37</v>
       </c>
       <c r="C26" s="7">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="D26" s="7">
-        <v>37.5</v>
+        <v>38.049999999999997</v>
       </c>
       <c r="E26" s="7">
-        <v>35.700000000000003</v>
-      </c>
-      <c r="F26" s="8">
-        <v>-0.25</v>
-      </c>
-      <c r="G26" s="8">
-        <v>-0.67</v>
+        <v>36.200000000000003</v>
+      </c>
+      <c r="F26" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="G26" s="10">
+        <v>1.35</v>
       </c>
       <c r="H26" s="9">
-        <v>0.76100000000000001</v>
+        <v>0.81699999999999995</v>
       </c>
       <c r="I26" s="10">
-        <v>20.9</v>
-      </c>
-      <c r="J26" s="8">
-        <v>-5.8</v>
+        <v>7.29</v>
+      </c>
+      <c r="J26" s="10">
+        <v>9.4700000000000006</v>
       </c>
       <c r="K26" s="9">
-        <v>5.58</v>
+        <v>6.4</v>
       </c>
       <c r="L26" s="8">
-        <v>-24.3</v>
+        <v>-21.2</v>
       </c>
       <c r="M26" s="9">
-        <v>0.76100000000000001</v>
+        <v>0.81699999999999995</v>
       </c>
       <c r="N26" s="10">
-        <v>20.9</v>
-      </c>
-      <c r="O26" s="8">
-        <v>-5.8</v>
+        <v>7.29</v>
+      </c>
+      <c r="O26" s="10">
+        <v>9.4700000000000006</v>
       </c>
       <c r="P26" s="9">
-        <v>5.58</v>
+        <v>6.4</v>
       </c>
       <c r="Q26" s="8">
-        <v>-24.3</v>
+        <v>-21.2</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B27" s="7">
-        <v>40.75</v>
+        <v>37</v>
       </c>
       <c r="C27" s="7">
-        <v>37.25</v>
+        <v>37</v>
       </c>
       <c r="D27" s="7">
-        <v>46.5</v>
+        <v>37.5</v>
       </c>
       <c r="E27" s="7">
-        <v>36.200000000000003</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="F27" s="8">
-        <v>-3.5</v>
+        <v>-0.25</v>
       </c>
       <c r="G27" s="8">
-        <v>-8.59</v>
+        <v>-0.67</v>
       </c>
       <c r="H27" s="9">
-        <v>0.63</v>
-      </c>
-      <c r="I27" s="8">
-        <v>-14.5</v>
+        <v>0.76100000000000001</v>
+      </c>
+      <c r="I27" s="10">
+        <v>20.9</v>
       </c>
       <c r="J27" s="8">
-        <v>-29</v>
+        <v>-5.8</v>
       </c>
       <c r="K27" s="9">
-        <v>4.82</v>
+        <v>5.58</v>
       </c>
       <c r="L27" s="8">
-        <v>-26.6</v>
+        <v>-24.3</v>
       </c>
       <c r="M27" s="9">
-        <v>0.63</v>
-      </c>
-      <c r="N27" s="8">
-        <v>-14.5</v>
+        <v>0.76100000000000001</v>
+      </c>
+      <c r="N27" s="10">
+        <v>20.9</v>
       </c>
       <c r="O27" s="8">
-        <v>-29</v>
+        <v>-5.8</v>
       </c>
       <c r="P27" s="9">
-        <v>4.82</v>
+        <v>5.58</v>
       </c>
       <c r="Q27" s="8">
-        <v>-26.6</v>
+        <v>-24.3</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B28" s="7">
-        <v>42.5</v>
+        <v>40.75</v>
       </c>
       <c r="C28" s="7">
-        <v>40.75</v>
+        <v>37.25</v>
       </c>
       <c r="D28" s="7">
-        <v>45.75</v>
+        <v>46.5</v>
       </c>
       <c r="E28" s="7">
-        <v>39.6</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="F28" s="8">
-        <v>-1.05</v>
+        <v>-3.5</v>
       </c>
       <c r="G28" s="8">
-        <v>-2.5099999999999998</v>
+        <v>-8.59</v>
       </c>
       <c r="H28" s="9">
-        <v>0.73699999999999999</v>
-      </c>
-      <c r="I28" s="10">
-        <v>36.9</v>
+        <v>0.63</v>
+      </c>
+      <c r="I28" s="8">
+        <v>-14.5</v>
       </c>
       <c r="J28" s="8">
-        <v>-21.5</v>
+        <v>-29</v>
       </c>
       <c r="K28" s="9">
-        <v>4.1900000000000004</v>
+        <v>4.82</v>
       </c>
       <c r="L28" s="8">
-        <v>-26.2</v>
+        <v>-26.6</v>
       </c>
       <c r="M28" s="9">
-        <v>0.73699999999999999</v>
-      </c>
-      <c r="N28" s="10">
-        <v>36.9</v>
+        <v>0.63</v>
+      </c>
+      <c r="N28" s="8">
+        <v>-14.5</v>
       </c>
       <c r="O28" s="8">
-        <v>-21.5</v>
+        <v>-29</v>
       </c>
       <c r="P28" s="9">
-        <v>4.1900000000000004</v>
+        <v>4.82</v>
       </c>
       <c r="Q28" s="8">
-        <v>-26.2</v>
+        <v>-26.6</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B29" s="7">
-        <v>39.299999999999997</v>
+        <v>42.5</v>
       </c>
       <c r="C29" s="7">
-        <v>41.8</v>
+        <v>40.75</v>
       </c>
       <c r="D29" s="7">
-        <v>50</v>
+        <v>45.75</v>
       </c>
       <c r="E29" s="7">
-        <v>38</v>
-      </c>
-      <c r="F29" s="10">
-        <v>2.35</v>
-      </c>
-      <c r="G29" s="10">
-        <v>5.96</v>
+        <v>39.6</v>
+      </c>
+      <c r="F29" s="8">
+        <v>-1.05</v>
+      </c>
+      <c r="G29" s="8">
+        <v>-2.5099999999999998</v>
       </c>
       <c r="H29" s="9">
-        <v>0.53800000000000003</v>
-      </c>
-      <c r="I29" s="8">
-        <v>-11.5</v>
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="I29" s="10">
+        <v>36.9</v>
       </c>
       <c r="J29" s="8">
-        <v>-46.4</v>
+        <v>-21.5</v>
       </c>
       <c r="K29" s="9">
-        <v>3.46</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="L29" s="8">
-        <v>-27.1</v>
+        <v>-26.2</v>
       </c>
       <c r="M29" s="9">
-        <v>0.53800000000000003</v>
-      </c>
-      <c r="N29" s="8">
-        <v>-11.5</v>
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="N29" s="10">
+        <v>36.9</v>
       </c>
       <c r="O29" s="8">
-        <v>-46.4</v>
+        <v>-21.5</v>
       </c>
       <c r="P29" s="9">
-        <v>3.46</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="Q29" s="8">
-        <v>-27.1</v>
+        <v>-26.2</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B30" s="7">
-        <v>37.5</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="C30" s="7">
-        <v>39.450000000000003</v>
+        <v>41.8</v>
       </c>
       <c r="D30" s="7">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E30" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F30" s="10">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="G30" s="10">
-        <v>8.3800000000000008</v>
+        <v>5.96</v>
       </c>
       <c r="H30" s="9">
-        <v>0.60799999999999998</v>
+        <v>0.53800000000000003</v>
       </c>
       <c r="I30" s="8">
-        <v>-32.1</v>
+        <v>-11.5</v>
       </c>
       <c r="J30" s="8">
-        <v>-39.5</v>
+        <v>-46.4</v>
       </c>
       <c r="K30" s="9">
-        <v>2.92</v>
+        <v>3.46</v>
       </c>
       <c r="L30" s="8">
-        <v>-21.9</v>
+        <v>-27.1</v>
       </c>
       <c r="M30" s="9">
-        <v>0.60799999999999998</v>
+        <v>0.53800000000000003</v>
       </c>
       <c r="N30" s="8">
-        <v>-32.1</v>
+        <v>-11.5</v>
       </c>
       <c r="O30" s="8">
-        <v>-39.5</v>
+        <v>-46.4</v>
       </c>
       <c r="P30" s="9">
-        <v>2.92</v>
+        <v>3.46</v>
       </c>
       <c r="Q30" s="8">
-        <v>-21.9</v>
+        <v>-27.1</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B31" s="7">
-        <v>42.15</v>
+        <v>37.5</v>
       </c>
       <c r="C31" s="7">
-        <v>36.4</v>
+        <v>39.450000000000003</v>
       </c>
       <c r="D31" s="7">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E31" s="7">
-        <v>29.25</v>
+        <v>37</v>
       </c>
       <c r="F31" s="10">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="G31" s="10">
-        <v>4</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="H31" s="9">
-        <v>0.89600000000000002</v>
-      </c>
-      <c r="I31" s="10">
-        <v>42.7</v>
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="I31" s="8">
+        <v>-32.1</v>
       </c>
       <c r="J31" s="8">
-        <v>-12</v>
+        <v>-39.5</v>
       </c>
       <c r="K31" s="9">
-        <v>2.31</v>
+        <v>2.92</v>
       </c>
       <c r="L31" s="8">
-        <v>-15.4</v>
+        <v>-21.9</v>
       </c>
       <c r="M31" s="9">
-        <v>0.89600000000000002</v>
-      </c>
-      <c r="N31" s="10">
-        <v>42.7</v>
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="N31" s="8">
+        <v>-32.1</v>
       </c>
       <c r="O31" s="8">
-        <v>-12</v>
+        <v>-39.5</v>
       </c>
       <c r="P31" s="9">
-        <v>2.31</v>
+        <v>2.92</v>
       </c>
       <c r="Q31" s="8">
-        <v>-15.4</v>
+        <v>-21.9</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43862</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>17</v>
+        <v>43891</v>
+      </c>
+      <c r="B32" s="7">
+        <v>42.15</v>
+      </c>
+      <c r="C32" s="7">
+        <v>36.4</v>
+      </c>
+      <c r="D32" s="7">
+        <v>46</v>
+      </c>
+      <c r="E32" s="7">
+        <v>29.25</v>
+      </c>
+      <c r="F32" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="G32" s="10">
+        <v>4</v>
       </c>
       <c r="H32" s="9">
-        <v>0.628</v>
-      </c>
-      <c r="I32" s="8">
-        <v>-20.100000000000001</v>
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="I32" s="10">
+        <v>42.7</v>
       </c>
       <c r="J32" s="8">
-        <v>-8.77</v>
+        <v>-12</v>
       </c>
       <c r="K32" s="9">
-        <v>1.41</v>
+        <v>2.31</v>
       </c>
       <c r="L32" s="8">
-        <v>-17.399999999999999</v>
+        <v>-15.4</v>
       </c>
       <c r="M32" s="9">
-        <v>0.628</v>
-      </c>
-      <c r="N32" s="8">
-        <v>-20.100000000000001</v>
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="N32" s="10">
+        <v>42.7</v>
       </c>
       <c r="O32" s="8">
-        <v>-8.77</v>
+        <v>-12</v>
       </c>
       <c r="P32" s="9">
-        <v>1.41</v>
+        <v>2.31</v>
       </c>
       <c r="Q32" s="8">
-        <v>-17.399999999999999</v>
+        <v>-15.4</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>17</v>
@@ -2889,33 +2889,86 @@
         <v>17</v>
       </c>
       <c r="H33" s="9">
+        <v>0.628</v>
+      </c>
+      <c r="I33" s="8">
+        <v>-20.100000000000001</v>
+      </c>
+      <c r="J33" s="8">
+        <v>-8.77</v>
+      </c>
+      <c r="K33" s="9">
+        <v>1.41</v>
+      </c>
+      <c r="L33" s="8">
+        <v>-17.399999999999999</v>
+      </c>
+      <c r="M33" s="9">
+        <v>0.628</v>
+      </c>
+      <c r="N33" s="8">
+        <v>-20.100000000000001</v>
+      </c>
+      <c r="O33" s="8">
+        <v>-8.77</v>
+      </c>
+      <c r="P33" s="9">
+        <v>1.41</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>-17.399999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>43831</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H34" s="9">
         <v>0.78600000000000003</v>
       </c>
-      <c r="I33" s="9" t="s">
+      <c r="I34" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J33" s="8">
+      <c r="J34" s="8">
         <v>-23.2</v>
       </c>
-      <c r="K33" s="9">
+      <c r="K34" s="9">
         <v>0.78600000000000003</v>
       </c>
-      <c r="L33" s="8">
+      <c r="L34" s="8">
         <v>-23.2</v>
       </c>
-      <c r="M33" s="9">
+      <c r="M34" s="9">
         <v>0.78600000000000003</v>
       </c>
-      <c r="N33" s="9" t="s">
+      <c r="N34" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O33" s="8">
+      <c r="O34" s="8">
         <v>-23.2</v>
       </c>
-      <c r="P33" s="9">
+      <c r="P34" s="9">
         <v>0.78600000000000003</v>
       </c>
-      <c r="Q33" s="8">
+      <c r="Q34" s="8">
         <v>-23.2</v>
       </c>
     </row>
